--- a/artfynd/A 33262-2024 artfynd.xlsx
+++ b/artfynd/A 33262-2024 artfynd.xlsx
@@ -2664,10 +2664,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119651678</v>
+        <v>119651641</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>91254</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2676,25 +2676,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477860</v>
+        <v>477881</v>
       </c>
       <c r="R21" t="n">
-        <v>7143097</v>
+        <v>7142847</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,11 +2740,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,10 +2766,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119651641</v>
+        <v>119651678</v>
       </c>
       <c r="B22" t="n">
-        <v>91254</v>
+        <v>57326</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,25 +2778,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2811,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477881</v>
+        <v>477860</v>
       </c>
       <c r="R22" t="n">
-        <v>7142847</v>
+        <v>7143097</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2847,6 +2842,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119651706</v>
+        <v>119651670</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3103,34 +3103,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478162</v>
+        <v>477861</v>
       </c>
       <c r="R25" t="n">
-        <v>7142400</v>
+        <v>7142701</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3189,10 +3205,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119651639</v>
+        <v>119651706</v>
       </c>
       <c r="B26" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3205,21 +3221,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3229,10 +3245,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478102</v>
+        <v>478162</v>
       </c>
       <c r="R26" t="n">
-        <v>7142644</v>
+        <v>7142400</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,10 +3307,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119651670</v>
+        <v>119651639</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3307,50 +3323,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477861</v>
+        <v>478102</v>
       </c>
       <c r="R27" t="n">
-        <v>7142701</v>
+        <v>7142644</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119651638</v>
+        <v>119651704</v>
       </c>
       <c r="B29" t="n">
-        <v>87406</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3532,21 +3532,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478188</v>
+        <v>478040</v>
       </c>
       <c r="R29" t="n">
-        <v>7142387</v>
+        <v>7142457</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,10 +3618,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119651704</v>
+        <v>119651638</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>87406</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3634,21 +3634,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478040</v>
+        <v>478188</v>
       </c>
       <c r="R30" t="n">
-        <v>7142457</v>
+        <v>7142387</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119651681</v>
+        <v>119651679</v>
       </c>
       <c r="B33" t="n">
-        <v>79607</v>
+        <v>57326</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3945,21 +3945,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478033</v>
+        <v>477695</v>
       </c>
       <c r="R33" t="n">
-        <v>7142718</v>
+        <v>7143155</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4005,6 +4005,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4031,10 +4036,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119651679</v>
+        <v>119651690</v>
       </c>
       <c r="B34" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4047,21 +4052,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4071,10 +4076,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477695</v>
+        <v>478032</v>
       </c>
       <c r="R34" t="n">
-        <v>7143155</v>
+        <v>7142707</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4107,11 +4112,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4138,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651690</v>
+        <v>119651698</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4154,21 +4154,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478032</v>
+        <v>477862</v>
       </c>
       <c r="R35" t="n">
-        <v>7142707</v>
+        <v>7142754</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651698</v>
+        <v>119651645</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4252,25 +4252,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477862</v>
+        <v>478034</v>
       </c>
       <c r="R36" t="n">
-        <v>7142754</v>
+        <v>7142532</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4342,10 +4342,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651645</v>
+        <v>119651685</v>
       </c>
       <c r="B37" t="n">
-        <v>91254</v>
+        <v>90558</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4354,25 +4354,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4382,10 +4382,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478034</v>
+        <v>478272</v>
       </c>
       <c r="R37" t="n">
-        <v>7142532</v>
+        <v>7142513</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4444,10 +4444,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651685</v>
+        <v>119651681</v>
       </c>
       <c r="B38" t="n">
-        <v>90558</v>
+        <v>79607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4460,21 +4460,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478272</v>
+        <v>478033</v>
       </c>
       <c r="R38" t="n">
-        <v>7142513</v>
+        <v>7142718</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5179,10 +5179,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651700</v>
+        <v>119651664</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5195,21 +5195,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477768</v>
+        <v>478157</v>
       </c>
       <c r="R45" t="n">
-        <v>7142610</v>
+        <v>7142616</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5255,6 +5255,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5281,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119651664</v>
+        <v>119651700</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5297,21 +5302,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5321,10 +5326,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478157</v>
+        <v>477768</v>
       </c>
       <c r="R46" t="n">
-        <v>7142616</v>
+        <v>7142610</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5357,11 +5362,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33262-2024 artfynd.xlsx
+++ b/artfynd/A 33262-2024 artfynd.xlsx
@@ -2664,10 +2664,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119651641</v>
+        <v>119651678</v>
       </c>
       <c r="B21" t="n">
-        <v>91254</v>
+        <v>57326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2676,25 +2676,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477881</v>
+        <v>477860</v>
       </c>
       <c r="R21" t="n">
-        <v>7142847</v>
+        <v>7143097</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,6 +2740,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2766,10 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119651678</v>
+        <v>119651641</v>
       </c>
       <c r="B22" t="n">
-        <v>57326</v>
+        <v>91254</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2778,25 +2783,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2806,10 +2811,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477860</v>
+        <v>477881</v>
       </c>
       <c r="R22" t="n">
-        <v>7143097</v>
+        <v>7142847</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,11 +2847,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3929,10 +3929,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119651679</v>
+        <v>119651681</v>
       </c>
       <c r="B33" t="n">
-        <v>57326</v>
+        <v>79607</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3945,21 +3945,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477695</v>
+        <v>478033</v>
       </c>
       <c r="R33" t="n">
-        <v>7143155</v>
+        <v>7142718</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4005,11 +4005,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4036,10 +4031,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119651690</v>
+        <v>119651679</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>57326</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4052,21 +4047,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4076,10 +4071,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478032</v>
+        <v>477695</v>
       </c>
       <c r="R34" t="n">
-        <v>7142707</v>
+        <v>7143155</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4112,6 +4107,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4138,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651698</v>
+        <v>119651690</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4154,21 +4154,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477862</v>
+        <v>478032</v>
       </c>
       <c r="R35" t="n">
-        <v>7142754</v>
+        <v>7142707</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651645</v>
+        <v>119651698</v>
       </c>
       <c r="B36" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4252,25 +4252,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478034</v>
+        <v>477862</v>
       </c>
       <c r="R36" t="n">
-        <v>7142532</v>
+        <v>7142754</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4342,10 +4342,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651685</v>
+        <v>119651645</v>
       </c>
       <c r="B37" t="n">
-        <v>90558</v>
+        <v>91254</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4354,25 +4354,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4382,10 +4382,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478272</v>
+        <v>478034</v>
       </c>
       <c r="R37" t="n">
-        <v>7142513</v>
+        <v>7142532</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4444,10 +4444,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651681</v>
+        <v>119651685</v>
       </c>
       <c r="B38" t="n">
-        <v>79607</v>
+        <v>90558</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4460,21 +4460,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478033</v>
+        <v>478272</v>
       </c>
       <c r="R38" t="n">
-        <v>7142718</v>
+        <v>7142513</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 33262-2024 artfynd.xlsx
+++ b/artfynd/A 33262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651676</v>
+        <v>119651706</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478329</v>
+        <v>478162</v>
       </c>
       <c r="R2" t="n">
-        <v>7142297</v>
+        <v>7142400</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651709</v>
+        <v>119651685</v>
       </c>
       <c r="B3" t="n">
-        <v>91128</v>
+        <v>90558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478183</v>
+        <v>478272</v>
       </c>
       <c r="R3" t="n">
-        <v>7142390</v>
+        <v>7142513</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651688</v>
+        <v>119651705</v>
       </c>
       <c r="B4" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477825</v>
+        <v>478087</v>
       </c>
       <c r="R4" t="n">
-        <v>7143049</v>
+        <v>7142484</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651699</v>
+        <v>119651694</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477616</v>
+        <v>477874</v>
       </c>
       <c r="R5" t="n">
-        <v>7142666</v>
+        <v>7142867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651695</v>
+        <v>119651671</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477953</v>
+        <v>478034</v>
       </c>
       <c r="R6" t="n">
-        <v>7142946</v>
+        <v>7142454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651696</v>
+        <v>119651641</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>91254</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478181</v>
+        <v>477881</v>
       </c>
       <c r="R7" t="n">
-        <v>7142430</v>
+        <v>7142847</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651691</v>
+        <v>119651682</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>57421</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,38 +1304,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477857</v>
+        <v>477848</v>
       </c>
       <c r="R8" t="n">
-        <v>7142825</v>
+        <v>7142542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651683</v>
+        <v>119651642</v>
       </c>
       <c r="B9" t="n">
-        <v>57421</v>
+        <v>91254</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,50 +1426,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478354</v>
+        <v>477886</v>
       </c>
       <c r="R9" t="n">
-        <v>7142310</v>
+        <v>7142880</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651644</v>
+        <v>119651707</v>
       </c>
       <c r="B10" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1524,25 +1524,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477632</v>
+        <v>478303</v>
       </c>
       <c r="R10" t="n">
-        <v>7142733</v>
+        <v>7142341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651708</v>
+        <v>119651697</v>
       </c>
       <c r="B11" t="n">
         <v>78526</v>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478398</v>
+        <v>478297</v>
       </c>
       <c r="R11" t="n">
-        <v>7142260</v>
+        <v>7142499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651707</v>
+        <v>119651676</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,21 +1732,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478303</v>
+        <v>478329</v>
       </c>
       <c r="R12" t="n">
-        <v>7142341</v>
+        <v>7142297</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,6 +1792,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1818,7 +1823,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651667</v>
+        <v>119651677</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1858,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477770</v>
+        <v>478328</v>
       </c>
       <c r="R13" t="n">
-        <v>7143140</v>
+        <v>7142289</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,7 +1903,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1925,7 +1930,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651671</v>
+        <v>119651674</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1965,10 +1970,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478034</v>
+        <v>478153</v>
       </c>
       <c r="R14" t="n">
-        <v>7142454</v>
+        <v>7142438</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2032,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651687</v>
+        <v>119651696</v>
       </c>
       <c r="B15" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2048,21 +2053,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2072,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477885</v>
+        <v>478181</v>
       </c>
       <c r="R15" t="n">
-        <v>7142877</v>
+        <v>7142430</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2134,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651697</v>
+        <v>119651691</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,21 +2155,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2174,10 +2179,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478297</v>
+        <v>477857</v>
       </c>
       <c r="R16" t="n">
-        <v>7142499</v>
+        <v>7142825</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651705</v>
+        <v>119651678</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2252,21 +2257,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2281,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478087</v>
+        <v>477860</v>
       </c>
       <c r="R17" t="n">
-        <v>7142484</v>
+        <v>7143097</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,6 +2317,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119651675</v>
+        <v>119651679</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2354,16 +2364,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2371,37 +2381,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478361</v>
+        <v>477695</v>
       </c>
       <c r="R18" t="n">
-        <v>7142354</v>
+        <v>7143155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,6 +2424,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2460,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119651701</v>
+        <v>119651688</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2476,21 +2471,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2500,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477873</v>
+        <v>477825</v>
       </c>
       <c r="R19" t="n">
-        <v>7142534</v>
+        <v>7143049</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,7 +2557,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119651689</v>
+        <v>119651690</v>
       </c>
       <c r="B20" t="n">
         <v>90580</v>
@@ -2602,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478214</v>
+        <v>478032</v>
       </c>
       <c r="R20" t="n">
-        <v>7142533</v>
+        <v>7142707</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119651678</v>
+        <v>119651695</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2680,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2704,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477860</v>
+        <v>477953</v>
       </c>
       <c r="R21" t="n">
-        <v>7143097</v>
+        <v>7142946</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,11 +2735,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2771,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119651641</v>
+        <v>119651704</v>
       </c>
       <c r="B22" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,25 +2773,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2811,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477881</v>
+        <v>478040</v>
       </c>
       <c r="R22" t="n">
-        <v>7142847</v>
+        <v>7142457</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,7 +2863,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119651668</v>
+        <v>119651666</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2913,10 +2903,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477695</v>
+        <v>477775</v>
       </c>
       <c r="R23" t="n">
-        <v>7142939</v>
+        <v>7143155</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,7 +2943,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2980,7 +2970,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119651674</v>
+        <v>119651668</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3020,10 +3010,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478153</v>
+        <v>477695</v>
       </c>
       <c r="R24" t="n">
-        <v>7142438</v>
+        <v>7142939</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3060,7 +3050,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3087,10 +3077,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119651670</v>
+        <v>119651646</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3099,54 +3089,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477861</v>
+        <v>478074</v>
       </c>
       <c r="R25" t="n">
-        <v>7142701</v>
+        <v>7142501</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3205,7 +3179,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119651706</v>
+        <v>119651698</v>
       </c>
       <c r="B26" t="n">
         <v>78526</v>
@@ -3245,10 +3219,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478162</v>
+        <v>477862</v>
       </c>
       <c r="R26" t="n">
-        <v>7142400</v>
+        <v>7142754</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,10 +3281,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119651639</v>
+        <v>119651665</v>
       </c>
       <c r="B27" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3323,21 +3297,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3347,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478102</v>
+        <v>477656</v>
       </c>
       <c r="R27" t="n">
-        <v>7142644</v>
+        <v>7143131</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,10 +3383,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119651669</v>
+        <v>119651638</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,21 +3399,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477624</v>
+        <v>478188</v>
       </c>
       <c r="R28" t="n">
-        <v>7142669</v>
+        <v>7142387</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,11 +3459,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3516,7 +3485,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119651704</v>
+        <v>119651701</v>
       </c>
       <c r="B29" t="n">
         <v>78526</v>
@@ -3556,10 +3525,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478040</v>
+        <v>477873</v>
       </c>
       <c r="R29" t="n">
-        <v>7142457</v>
+        <v>7142534</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,10 +3587,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119651638</v>
+        <v>119651669</v>
       </c>
       <c r="B30" t="n">
-        <v>87406</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3634,21 +3603,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3658,10 +3627,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478188</v>
+        <v>477624</v>
       </c>
       <c r="R30" t="n">
-        <v>7142387</v>
+        <v>7142669</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3694,6 +3663,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3720,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119651666</v>
+        <v>119651699</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3736,21 +3710,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3760,10 +3734,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477775</v>
+        <v>477616</v>
       </c>
       <c r="R31" t="n">
-        <v>7143155</v>
+        <v>7142666</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3796,11 +3770,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3827,10 +3796,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119651646</v>
+        <v>119651683</v>
       </c>
       <c r="B32" t="n">
-        <v>91254</v>
+        <v>57421</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3843,34 +3812,50 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478074</v>
+        <v>478354</v>
       </c>
       <c r="R32" t="n">
-        <v>7142501</v>
+        <v>7142310</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,10 +3914,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119651681</v>
+        <v>119651670</v>
       </c>
       <c r="B33" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3945,34 +3930,50 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478033</v>
+        <v>477861</v>
       </c>
       <c r="R33" t="n">
-        <v>7142718</v>
+        <v>7142701</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4031,10 +4032,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119651679</v>
+        <v>119651709</v>
       </c>
       <c r="B34" t="n">
-        <v>57326</v>
+        <v>91128</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4043,25 +4044,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>760</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4071,10 +4072,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477695</v>
+        <v>478183</v>
       </c>
       <c r="R34" t="n">
-        <v>7143155</v>
+        <v>7142390</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4107,11 +4108,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4138,10 +4134,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651690</v>
+        <v>119651664</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4154,21 +4150,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4178,10 +4174,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478032</v>
+        <v>478157</v>
       </c>
       <c r="R35" t="n">
-        <v>7142707</v>
+        <v>7142616</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4214,6 +4210,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4240,10 +4241,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651698</v>
+        <v>119651643</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4252,25 +4253,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4280,10 +4281,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477862</v>
+        <v>477621</v>
       </c>
       <c r="R36" t="n">
-        <v>7142754</v>
+        <v>7142895</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4342,10 +4343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651645</v>
+        <v>119651689</v>
       </c>
       <c r="B37" t="n">
-        <v>91254</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4354,25 +4355,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4382,10 +4383,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478034</v>
+        <v>478214</v>
       </c>
       <c r="R37" t="n">
-        <v>7142532</v>
+        <v>7142533</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4444,10 +4445,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651685</v>
+        <v>119651639</v>
       </c>
       <c r="B38" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4460,21 +4461,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4484,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478272</v>
+        <v>478102</v>
       </c>
       <c r="R38" t="n">
-        <v>7142513</v>
+        <v>7142644</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4546,10 +4547,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119651694</v>
+        <v>119651645</v>
       </c>
       <c r="B39" t="n">
-        <v>90580</v>
+        <v>91254</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4558,25 +4559,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4586,10 +4587,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477874</v>
+        <v>478034</v>
       </c>
       <c r="R39" t="n">
-        <v>7142867</v>
+        <v>7142532</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4648,10 +4649,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119651642</v>
+        <v>119651700</v>
       </c>
       <c r="B40" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4660,25 +4661,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4688,10 +4689,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477886</v>
+        <v>477768</v>
       </c>
       <c r="R40" t="n">
-        <v>7142880</v>
+        <v>7142610</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4750,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119651643</v>
+        <v>119651687</v>
       </c>
       <c r="B41" t="n">
-        <v>91254</v>
+        <v>90558</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4762,25 +4763,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4790,10 +4791,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477621</v>
+        <v>477885</v>
       </c>
       <c r="R41" t="n">
-        <v>7142895</v>
+        <v>7142877</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4852,10 +4853,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119651682</v>
+        <v>119651708</v>
       </c>
       <c r="B42" t="n">
-        <v>57421</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4864,54 +4865,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477848</v>
+        <v>478398</v>
       </c>
       <c r="R42" t="n">
-        <v>7142542</v>
+        <v>7142260</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4970,7 +4955,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119651665</v>
+        <v>119651675</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5003,17 +4988,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477656</v>
+        <v>478361</v>
       </c>
       <c r="R43" t="n">
-        <v>7143131</v>
+        <v>7142354</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5072,10 +5077,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119651677</v>
+        <v>119651644</v>
       </c>
       <c r="B44" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5084,25 +5089,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5112,10 +5117,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478328</v>
+        <v>477632</v>
       </c>
       <c r="R44" t="n">
-        <v>7142289</v>
+        <v>7142733</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5148,11 +5153,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5179,10 +5179,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651664</v>
+        <v>119651681</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5195,21 +5195,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478157</v>
+        <v>478033</v>
       </c>
       <c r="R45" t="n">
-        <v>7142616</v>
+        <v>7142718</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5255,11 +5255,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5286,10 +5281,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119651700</v>
+        <v>119651667</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5302,21 +5297,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5326,10 +5321,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477768</v>
+        <v>477770</v>
       </c>
       <c r="R46" t="n">
-        <v>7142610</v>
+        <v>7143140</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5362,6 +5357,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33262-2024 artfynd.xlsx
+++ b/artfynd/A 33262-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651706</v>
+        <v>119651698</v>
       </c>
       <c r="B2" t="n">
         <v>78526</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478162</v>
+        <v>477862</v>
       </c>
       <c r="R2" t="n">
-        <v>7142400</v>
+        <v>7142754</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651685</v>
+        <v>119651646</v>
       </c>
       <c r="B3" t="n">
-        <v>90558</v>
+        <v>91254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478272</v>
+        <v>478074</v>
       </c>
       <c r="R3" t="n">
-        <v>7142513</v>
+        <v>7142501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651705</v>
+        <v>119651687</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478087</v>
+        <v>477885</v>
       </c>
       <c r="R4" t="n">
-        <v>7142484</v>
+        <v>7142877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651694</v>
+        <v>119651676</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477874</v>
+        <v>478329</v>
       </c>
       <c r="R5" t="n">
-        <v>7142867</v>
+        <v>7142297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651671</v>
+        <v>119651701</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478034</v>
+        <v>477873</v>
       </c>
       <c r="R6" t="n">
-        <v>7142454</v>
+        <v>7142534</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651641</v>
+        <v>119651697</v>
       </c>
       <c r="B7" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477881</v>
+        <v>478297</v>
       </c>
       <c r="R7" t="n">
-        <v>7142847</v>
+        <v>7142499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651682</v>
+        <v>119651675</v>
       </c>
       <c r="B8" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,20 +1304,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1327,11 +1327,15 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1348,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477848</v>
+        <v>478361</v>
       </c>
       <c r="R8" t="n">
-        <v>7142542</v>
+        <v>7142354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651642</v>
+        <v>119651705</v>
       </c>
       <c r="B9" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1450,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477886</v>
+        <v>478087</v>
       </c>
       <c r="R9" t="n">
-        <v>7142880</v>
+        <v>7142484</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651707</v>
+        <v>119651683</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>57421</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1524,38 +1528,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478303</v>
+        <v>478354</v>
       </c>
       <c r="R10" t="n">
-        <v>7142341</v>
+        <v>7142310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651697</v>
+        <v>119651709</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>91128</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478297</v>
+        <v>478183</v>
       </c>
       <c r="R11" t="n">
-        <v>7142499</v>
+        <v>7142390</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651676</v>
+        <v>119651689</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478329</v>
+        <v>478214</v>
       </c>
       <c r="R12" t="n">
-        <v>7142297</v>
+        <v>7142533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,11 +1812,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,7 +1838,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651677</v>
+        <v>119651667</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1863,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478328</v>
+        <v>477770</v>
       </c>
       <c r="R13" t="n">
-        <v>7142289</v>
+        <v>7143140</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,7 +1918,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,7 +1945,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651674</v>
+        <v>119651664</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1970,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478153</v>
+        <v>478157</v>
       </c>
       <c r="R14" t="n">
-        <v>7142438</v>
+        <v>7142616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,7 +2025,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2037,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651696</v>
+        <v>119651704</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,21 +2068,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478181</v>
+        <v>478040</v>
       </c>
       <c r="R15" t="n">
-        <v>7142430</v>
+        <v>7142457</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,7 +2154,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651691</v>
+        <v>119651695</v>
       </c>
       <c r="B16" t="n">
         <v>90580</v>
@@ -2179,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477857</v>
+        <v>477953</v>
       </c>
       <c r="R16" t="n">
-        <v>7142825</v>
+        <v>7142946</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651678</v>
+        <v>119651691</v>
       </c>
       <c r="B17" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2257,21 +2272,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2281,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477860</v>
+        <v>477857</v>
       </c>
       <c r="R17" t="n">
-        <v>7143097</v>
+        <v>7142825</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,11 +2332,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2348,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119651679</v>
+        <v>119651642</v>
       </c>
       <c r="B18" t="n">
-        <v>57326</v>
+        <v>91254</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2360,25 +2370,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477695</v>
+        <v>477886</v>
       </c>
       <c r="R18" t="n">
-        <v>7143155</v>
+        <v>7142880</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,11 +2434,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2455,10 +2460,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119651688</v>
+        <v>119651677</v>
       </c>
       <c r="B19" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,21 +2476,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477825</v>
+        <v>478328</v>
       </c>
       <c r="R19" t="n">
-        <v>7143049</v>
+        <v>7142289</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,6 +2536,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2557,10 +2567,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119651690</v>
+        <v>119651671</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2573,21 +2583,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2607,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478032</v>
+        <v>478034</v>
       </c>
       <c r="R20" t="n">
-        <v>7142707</v>
+        <v>7142454</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,6 +2643,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,10 +2674,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119651695</v>
+        <v>119651688</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,21 +2690,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477953</v>
+        <v>477825</v>
       </c>
       <c r="R21" t="n">
-        <v>7142946</v>
+        <v>7143049</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,10 +2776,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119651704</v>
+        <v>119651681</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2777,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2801,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478040</v>
+        <v>478033</v>
       </c>
       <c r="R22" t="n">
-        <v>7142457</v>
+        <v>7142718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,10 +2985,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119651668</v>
+        <v>119651699</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2986,21 +3001,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,10 +3025,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477695</v>
+        <v>477616</v>
       </c>
       <c r="R24" t="n">
-        <v>7142939</v>
+        <v>7142666</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,11 +3061,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3077,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119651646</v>
+        <v>119651670</v>
       </c>
       <c r="B25" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3089,38 +3099,54 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478074</v>
+        <v>477861</v>
       </c>
       <c r="R25" t="n">
-        <v>7142501</v>
+        <v>7142701</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,7 +3205,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119651698</v>
+        <v>119651700</v>
       </c>
       <c r="B26" t="n">
         <v>78526</v>
@@ -3219,10 +3245,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477862</v>
+        <v>477768</v>
       </c>
       <c r="R26" t="n">
-        <v>7142754</v>
+        <v>7142610</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,10 +3307,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119651665</v>
+        <v>119651638</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>87406</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3297,21 +3323,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3321,10 +3347,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477656</v>
+        <v>478188</v>
       </c>
       <c r="R27" t="n">
-        <v>7143131</v>
+        <v>7142387</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3383,10 +3409,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119651638</v>
+        <v>119651665</v>
       </c>
       <c r="B28" t="n">
-        <v>87406</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3399,21 +3425,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3423,10 +3449,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478188</v>
+        <v>477656</v>
       </c>
       <c r="R28" t="n">
-        <v>7142387</v>
+        <v>7143131</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,10 +3511,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119651701</v>
+        <v>119651674</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3501,21 +3527,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3525,10 +3551,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477873</v>
+        <v>478153</v>
       </c>
       <c r="R29" t="n">
-        <v>7142534</v>
+        <v>7142438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3561,6 +3587,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3587,10 +3618,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119651669</v>
+        <v>119651708</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3603,21 +3634,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3627,10 +3658,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477624</v>
+        <v>478398</v>
       </c>
       <c r="R30" t="n">
-        <v>7142669</v>
+        <v>7142260</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3663,11 +3694,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3694,10 +3720,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119651699</v>
+        <v>119651696</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3710,21 +3736,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3734,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477616</v>
+        <v>478181</v>
       </c>
       <c r="R31" t="n">
-        <v>7142666</v>
+        <v>7142430</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3796,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119651683</v>
+        <v>119651694</v>
       </c>
       <c r="B32" t="n">
-        <v>57421</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3808,54 +3834,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478354</v>
+        <v>477874</v>
       </c>
       <c r="R32" t="n">
-        <v>7142310</v>
+        <v>7142867</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3914,10 +3924,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119651670</v>
+        <v>119651706</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3930,50 +3940,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477861</v>
+        <v>478162</v>
       </c>
       <c r="R33" t="n">
-        <v>7142701</v>
+        <v>7142400</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4032,10 +4026,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119651709</v>
+        <v>119651678</v>
       </c>
       <c r="B34" t="n">
-        <v>91128</v>
+        <v>57326</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4044,25 +4038,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4072,10 +4066,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478183</v>
+        <v>477860</v>
       </c>
       <c r="R34" t="n">
-        <v>7142390</v>
+        <v>7143097</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4108,6 +4102,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4134,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651664</v>
+        <v>119651690</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4150,21 +4149,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4174,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478157</v>
+        <v>478032</v>
       </c>
       <c r="R35" t="n">
-        <v>7142616</v>
+        <v>7142707</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4210,11 +4209,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4241,10 +4235,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651643</v>
+        <v>119651639</v>
       </c>
       <c r="B36" t="n">
-        <v>91254</v>
+        <v>90562</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4253,25 +4247,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4281,10 +4275,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477621</v>
+        <v>478102</v>
       </c>
       <c r="R36" t="n">
-        <v>7142895</v>
+        <v>7142644</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4343,10 +4337,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651689</v>
+        <v>119651641</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>91254</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4355,25 +4349,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4383,10 +4377,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478214</v>
+        <v>477881</v>
       </c>
       <c r="R37" t="n">
-        <v>7142533</v>
+        <v>7142847</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4445,10 +4439,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651639</v>
+        <v>119651645</v>
       </c>
       <c r="B38" t="n">
-        <v>90562</v>
+        <v>91254</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4457,25 +4451,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,10 +4479,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478102</v>
+        <v>478034</v>
       </c>
       <c r="R38" t="n">
-        <v>7142644</v>
+        <v>7142532</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4547,10 +4541,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119651645</v>
+        <v>119651669</v>
       </c>
       <c r="B39" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4559,25 +4553,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4587,10 +4581,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478034</v>
+        <v>477624</v>
       </c>
       <c r="R39" t="n">
-        <v>7142532</v>
+        <v>7142669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4623,6 +4617,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4649,10 +4648,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119651700</v>
+        <v>119651668</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4665,21 +4664,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4689,10 +4688,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477768</v>
+        <v>477695</v>
       </c>
       <c r="R40" t="n">
-        <v>7142610</v>
+        <v>7142939</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4725,6 +4724,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4751,10 +4755,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119651687</v>
+        <v>119651679</v>
       </c>
       <c r="B41" t="n">
-        <v>90558</v>
+        <v>57326</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4767,21 +4771,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4791,10 +4795,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477885</v>
+        <v>477695</v>
       </c>
       <c r="R41" t="n">
-        <v>7142877</v>
+        <v>7143155</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4827,6 +4831,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4853,10 +4862,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119651708</v>
+        <v>119651643</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4865,25 +4874,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4893,10 +4902,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478398</v>
+        <v>477621</v>
       </c>
       <c r="R42" t="n">
-        <v>7142260</v>
+        <v>7142895</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4955,10 +4964,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119651675</v>
+        <v>119651644</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4967,58 +4976,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478361</v>
+        <v>477632</v>
       </c>
       <c r="R43" t="n">
-        <v>7142354</v>
+        <v>7142733</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5077,10 +5066,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119651644</v>
+        <v>119651707</v>
       </c>
       <c r="B44" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5089,25 +5078,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5117,10 +5106,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477632</v>
+        <v>478303</v>
       </c>
       <c r="R44" t="n">
-        <v>7142733</v>
+        <v>7142341</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5179,10 +5168,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651681</v>
+        <v>119651685</v>
       </c>
       <c r="B45" t="n">
-        <v>79607</v>
+        <v>90558</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5195,21 +5184,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5219,10 +5208,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478033</v>
+        <v>478272</v>
       </c>
       <c r="R45" t="n">
-        <v>7142718</v>
+        <v>7142513</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5281,10 +5270,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119651667</v>
+        <v>119651682</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5293,20 +5282,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5314,17 +5303,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477770</v>
+        <v>477848</v>
       </c>
       <c r="R46" t="n">
-        <v>7143140</v>
+        <v>7142542</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5357,11 +5362,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 33262-2024 artfynd.xlsx
+++ b/artfynd/A 33262-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651646</v>
+        <v>119651687</v>
       </c>
       <c r="B3" t="n">
-        <v>91254</v>
+        <v>90558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478074</v>
+        <v>477885</v>
       </c>
       <c r="R3" t="n">
-        <v>7142501</v>
+        <v>7142877</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651687</v>
+        <v>119651646</v>
       </c>
       <c r="B4" t="n">
-        <v>90558</v>
+        <v>91254</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477885</v>
+        <v>478074</v>
       </c>
       <c r="R4" t="n">
-        <v>7142877</v>
+        <v>7142501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651675</v>
+        <v>119651705</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,54 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478361</v>
+        <v>478087</v>
       </c>
       <c r="R8" t="n">
-        <v>7142354</v>
+        <v>7142484</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651705</v>
+        <v>119651675</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,34 +1410,54 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478087</v>
+        <v>478361</v>
       </c>
       <c r="R9" t="n">
-        <v>7142484</v>
+        <v>7142354</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -4862,7 +4862,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119651643</v>
+        <v>119651644</v>
       </c>
       <c r="B42" t="n">
         <v>91254</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477621</v>
+        <v>477632</v>
       </c>
       <c r="R42" t="n">
-        <v>7142895</v>
+        <v>7142733</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119651644</v>
+        <v>119651643</v>
       </c>
       <c r="B43" t="n">
         <v>91254</v>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477632</v>
+        <v>477621</v>
       </c>
       <c r="R43" t="n">
-        <v>7142733</v>
+        <v>7142895</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 33262-2024 artfynd.xlsx
+++ b/artfynd/A 33262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651698</v>
+        <v>119651669</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477862</v>
+        <v>477624</v>
       </c>
       <c r="R2" t="n">
-        <v>7142754</v>
+        <v>7142669</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651687</v>
+        <v>119651678</v>
       </c>
       <c r="B3" t="n">
-        <v>90558</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477885</v>
+        <v>477860</v>
       </c>
       <c r="R3" t="n">
-        <v>7142877</v>
+        <v>7143097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651646</v>
+        <v>119651638</v>
       </c>
       <c r="B4" t="n">
-        <v>91254</v>
+        <v>87406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478074</v>
+        <v>478188</v>
       </c>
       <c r="R4" t="n">
-        <v>7142501</v>
+        <v>7142387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651676</v>
+        <v>119651644</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478329</v>
+        <v>477632</v>
       </c>
       <c r="R5" t="n">
-        <v>7142297</v>
+        <v>7142733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651701</v>
+        <v>119651709</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>91128</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477873</v>
+        <v>478183</v>
       </c>
       <c r="R6" t="n">
-        <v>7142534</v>
+        <v>7142390</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651697</v>
+        <v>119651708</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478297</v>
+        <v>478398</v>
       </c>
       <c r="R7" t="n">
-        <v>7142499</v>
+        <v>7142260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651705</v>
+        <v>119651707</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478087</v>
+        <v>478303</v>
       </c>
       <c r="R8" t="n">
-        <v>7142484</v>
+        <v>7142341</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651675</v>
+        <v>119651667</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1427,37 +1432,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478361</v>
+        <v>477770</v>
       </c>
       <c r="R9" t="n">
-        <v>7142354</v>
+        <v>7143140</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651683</v>
+        <v>119651665</v>
       </c>
       <c r="B10" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,20 +1518,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1549,33 +1539,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478354</v>
+        <v>477656</v>
       </c>
       <c r="R10" t="n">
-        <v>7142310</v>
+        <v>7143131</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651709</v>
+        <v>119651668</v>
       </c>
       <c r="B11" t="n">
-        <v>91128</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478183</v>
+        <v>477695</v>
       </c>
       <c r="R11" t="n">
-        <v>7142390</v>
+        <v>7142939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,6 +1684,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1736,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651689</v>
+        <v>119651679</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478214</v>
+        <v>477695</v>
       </c>
       <c r="R12" t="n">
-        <v>7142533</v>
+        <v>7143155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651667</v>
+        <v>119651705</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477770</v>
+        <v>478087</v>
       </c>
       <c r="R13" t="n">
-        <v>7143140</v>
+        <v>7142484</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651664</v>
+        <v>119651699</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1985,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478157</v>
+        <v>477616</v>
       </c>
       <c r="R14" t="n">
-        <v>7142616</v>
+        <v>7142666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,11 +2000,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651704</v>
+        <v>119651681</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2068,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478040</v>
+        <v>478033</v>
       </c>
       <c r="R15" t="n">
-        <v>7142457</v>
+        <v>7142718</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651695</v>
+        <v>119651685</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477953</v>
+        <v>478272</v>
       </c>
       <c r="R16" t="n">
-        <v>7142946</v>
+        <v>7142513</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651691</v>
+        <v>119651701</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2272,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477857</v>
+        <v>477873</v>
       </c>
       <c r="R17" t="n">
-        <v>7142825</v>
+        <v>7142534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119651642</v>
+        <v>119651683</v>
       </c>
       <c r="B18" t="n">
-        <v>91254</v>
+        <v>57421</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,34 +2348,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477886</v>
+        <v>478354</v>
       </c>
       <c r="R18" t="n">
-        <v>7142880</v>
+        <v>7142310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2460,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119651677</v>
+        <v>119651704</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2476,21 +2466,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2500,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478328</v>
+        <v>478040</v>
       </c>
       <c r="R19" t="n">
-        <v>7142289</v>
+        <v>7142457</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,11 +2526,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119651688</v>
+        <v>119651664</v>
       </c>
       <c r="B21" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2690,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2714,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477825</v>
+        <v>478157</v>
       </c>
       <c r="R21" t="n">
-        <v>7143049</v>
+        <v>7142616</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,6 +2735,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2776,10 +2766,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119651681</v>
+        <v>119651639</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2792,21 +2782,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478033</v>
+        <v>478102</v>
       </c>
       <c r="R22" t="n">
-        <v>7142718</v>
+        <v>7142644</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2878,10 +2868,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119651666</v>
+        <v>119651687</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2894,21 +2884,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2908,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477775</v>
+        <v>477885</v>
       </c>
       <c r="R23" t="n">
-        <v>7143155</v>
+        <v>7142877</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2954,11 +2944,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2985,10 +2970,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119651699</v>
+        <v>119651675</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3001,34 +2986,54 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477616</v>
+        <v>478361</v>
       </c>
       <c r="R24" t="n">
-        <v>7142666</v>
+        <v>7142354</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,7 +3092,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119651670</v>
+        <v>119651666</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3120,33 +3125,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477861</v>
+        <v>477775</v>
       </c>
       <c r="R25" t="n">
-        <v>7142701</v>
+        <v>7143155</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,6 +3168,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3205,10 +3199,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119651700</v>
+        <v>119651642</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3217,25 +3211,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3245,10 +3239,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477768</v>
+        <v>477886</v>
       </c>
       <c r="R26" t="n">
-        <v>7142610</v>
+        <v>7142880</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119651638</v>
+        <v>119651695</v>
       </c>
       <c r="B27" t="n">
-        <v>87406</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3323,21 +3317,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4412</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3347,10 +3341,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478188</v>
+        <v>477953</v>
       </c>
       <c r="R27" t="n">
-        <v>7142387</v>
+        <v>7142946</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,10 +3403,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119651665</v>
+        <v>119651700</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3425,21 +3419,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3443,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477656</v>
+        <v>477768</v>
       </c>
       <c r="R28" t="n">
-        <v>7143131</v>
+        <v>7142610</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3511,7 +3505,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119651674</v>
+        <v>119651677</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3551,10 +3545,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478153</v>
+        <v>478328</v>
       </c>
       <c r="R29" t="n">
-        <v>7142438</v>
+        <v>7142289</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3591,7 +3585,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3618,10 +3612,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119651708</v>
+        <v>119651689</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3634,21 +3628,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3658,10 +3652,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478398</v>
+        <v>478214</v>
       </c>
       <c r="R30" t="n">
-        <v>7142260</v>
+        <v>7142533</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,7 +3714,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119651696</v>
+        <v>119651694</v>
       </c>
       <c r="B31" t="n">
         <v>90580</v>
@@ -3760,10 +3754,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478181</v>
+        <v>477874</v>
       </c>
       <c r="R31" t="n">
-        <v>7142430</v>
+        <v>7142867</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,10 +3816,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119651694</v>
+        <v>119651645</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>91254</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3834,25 +3828,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3862,10 +3856,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477874</v>
+        <v>478034</v>
       </c>
       <c r="R32" t="n">
-        <v>7142867</v>
+        <v>7142532</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,10 +3918,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119651706</v>
+        <v>119651676</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3940,21 +3934,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3964,10 +3958,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478162</v>
+        <v>478329</v>
       </c>
       <c r="R33" t="n">
-        <v>7142400</v>
+        <v>7142297</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4000,6 +3994,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4026,10 +4025,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119651678</v>
+        <v>119651696</v>
       </c>
       <c r="B34" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4042,21 +4041,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4066,10 +4065,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477860</v>
+        <v>478181</v>
       </c>
       <c r="R34" t="n">
-        <v>7143097</v>
+        <v>7142430</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4102,11 +4101,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4133,10 +4127,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651690</v>
+        <v>119651641</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>91254</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4145,25 +4139,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +4167,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478032</v>
+        <v>477881</v>
       </c>
       <c r="R35" t="n">
-        <v>7142707</v>
+        <v>7142847</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4235,10 +4229,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651639</v>
+        <v>119651706</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4251,21 +4245,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4275,10 +4269,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478102</v>
+        <v>478162</v>
       </c>
       <c r="R36" t="n">
-        <v>7142644</v>
+        <v>7142400</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4337,7 +4331,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651641</v>
+        <v>119651646</v>
       </c>
       <c r="B37" t="n">
         <v>91254</v>
@@ -4377,10 +4371,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477881</v>
+        <v>478074</v>
       </c>
       <c r="R37" t="n">
-        <v>7142847</v>
+        <v>7142501</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4439,10 +4433,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651645</v>
+        <v>119651690</v>
       </c>
       <c r="B38" t="n">
-        <v>91254</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4451,25 +4445,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4479,10 +4473,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478034</v>
+        <v>478032</v>
       </c>
       <c r="R38" t="n">
-        <v>7142532</v>
+        <v>7142707</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4541,10 +4535,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119651669</v>
+        <v>119651698</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4557,21 +4551,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4581,10 +4575,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477624</v>
+        <v>477862</v>
       </c>
       <c r="R39" t="n">
-        <v>7142669</v>
+        <v>7142754</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4617,11 +4611,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4648,10 +4637,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119651668</v>
+        <v>119651643</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4660,25 +4649,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4688,10 +4677,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477695</v>
+        <v>477621</v>
       </c>
       <c r="R40" t="n">
-        <v>7142939</v>
+        <v>7142895</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4724,11 +4713,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4755,10 +4739,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119651679</v>
+        <v>119651688</v>
       </c>
       <c r="B41" t="n">
-        <v>57326</v>
+        <v>90558</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4771,21 +4755,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4795,10 +4779,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477695</v>
+        <v>477825</v>
       </c>
       <c r="R41" t="n">
-        <v>7143155</v>
+        <v>7143049</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4831,11 +4815,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4862,10 +4841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119651644</v>
+        <v>119651697</v>
       </c>
       <c r="B42" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4874,25 +4853,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4902,10 +4881,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477632</v>
+        <v>478297</v>
       </c>
       <c r="R42" t="n">
-        <v>7142733</v>
+        <v>7142499</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4964,10 +4943,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119651643</v>
+        <v>119651670</v>
       </c>
       <c r="B43" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4976,38 +4955,54 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477621</v>
+        <v>477861</v>
       </c>
       <c r="R43" t="n">
-        <v>7142895</v>
+        <v>7142701</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5066,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119651707</v>
+        <v>119651674</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5082,21 +5077,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5106,10 +5101,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478303</v>
+        <v>478153</v>
       </c>
       <c r="R44" t="n">
-        <v>7142341</v>
+        <v>7142438</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5142,6 +5137,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5168,10 +5168,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651685</v>
+        <v>119651691</v>
       </c>
       <c r="B45" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5184,21 +5184,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478272</v>
+        <v>477857</v>
       </c>
       <c r="R45" t="n">
-        <v>7142513</v>
+        <v>7142825</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 33262-2024 artfynd.xlsx
+++ b/artfynd/A 33262-2024 artfynd.xlsx
@@ -4739,10 +4739,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119651688</v>
+        <v>119651691</v>
       </c>
       <c r="B41" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477825</v>
+        <v>477857</v>
       </c>
       <c r="R41" t="n">
-        <v>7143049</v>
+        <v>7142825</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119651697</v>
+        <v>119651688</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4857,21 +4857,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478297</v>
+        <v>477825</v>
       </c>
       <c r="R42" t="n">
-        <v>7142499</v>
+        <v>7143049</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4943,10 +4943,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119651670</v>
+        <v>119651697</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4959,50 +4959,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477861</v>
+        <v>478297</v>
       </c>
       <c r="R43" t="n">
-        <v>7142701</v>
+        <v>7142499</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5061,7 +5045,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119651674</v>
+        <v>119651670</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5094,17 +5078,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478153</v>
+        <v>477861</v>
       </c>
       <c r="R44" t="n">
-        <v>7142438</v>
+        <v>7142701</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5137,11 +5137,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5168,10 +5163,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651691</v>
+        <v>119651674</v>
       </c>
       <c r="B45" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5184,21 +5179,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5208,10 +5203,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477857</v>
+        <v>478153</v>
       </c>
       <c r="R45" t="n">
-        <v>7142825</v>
+        <v>7142438</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5244,6 +5239,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 33262-2024 artfynd.xlsx
+++ b/artfynd/A 33262-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651669</v>
+        <v>119651678</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477624</v>
+        <v>477860</v>
       </c>
       <c r="R2" t="n">
-        <v>7142669</v>
+        <v>7143097</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651678</v>
+        <v>119651669</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477860</v>
+        <v>477624</v>
       </c>
       <c r="R3" t="n">
-        <v>7143097</v>
+        <v>7142669</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -4127,10 +4127,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651641</v>
+        <v>119651706</v>
       </c>
       <c r="B35" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4139,25 +4139,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477881</v>
+        <v>478162</v>
       </c>
       <c r="R35" t="n">
-        <v>7142847</v>
+        <v>7142400</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651706</v>
+        <v>119651641</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4241,25 +4241,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478162</v>
+        <v>477881</v>
       </c>
       <c r="R36" t="n">
-        <v>7142400</v>
+        <v>7142847</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4739,10 +4739,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119651691</v>
+        <v>119651688</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4755,21 +4755,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477857</v>
+        <v>477825</v>
       </c>
       <c r="R41" t="n">
-        <v>7142825</v>
+        <v>7143049</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119651688</v>
+        <v>119651697</v>
       </c>
       <c r="B42" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4857,21 +4857,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477825</v>
+        <v>478297</v>
       </c>
       <c r="R42" t="n">
-        <v>7143049</v>
+        <v>7142499</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4943,10 +4943,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119651697</v>
+        <v>119651670</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4959,34 +4959,50 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478297</v>
+        <v>477861</v>
       </c>
       <c r="R43" t="n">
-        <v>7142499</v>
+        <v>7142701</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5045,7 +5061,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119651670</v>
+        <v>119651674</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5078,33 +5094,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477861</v>
+        <v>478153</v>
       </c>
       <c r="R44" t="n">
-        <v>7142701</v>
+        <v>7142438</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5137,6 +5137,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5163,10 +5168,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119651674</v>
+        <v>119651691</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5179,21 +5184,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5203,10 +5208,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478153</v>
+        <v>477857</v>
       </c>
       <c r="R45" t="n">
-        <v>7142438</v>
+        <v>7142825</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5239,11 +5244,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 33262-2024 artfynd.xlsx
+++ b/artfynd/A 33262-2024 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651638</v>
+        <v>119651709</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>91128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478188</v>
+        <v>478183</v>
       </c>
       <c r="R4" t="n">
-        <v>7142387</v>
+        <v>7142390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651644</v>
+        <v>119651638</v>
       </c>
       <c r="B5" t="n">
-        <v>91254</v>
+        <v>87406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477632</v>
+        <v>478188</v>
       </c>
       <c r="R5" t="n">
-        <v>7142733</v>
+        <v>7142387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651709</v>
+        <v>119651644</v>
       </c>
       <c r="B6" t="n">
-        <v>91128</v>
+        <v>91254</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478183</v>
+        <v>477632</v>
       </c>
       <c r="R6" t="n">
-        <v>7142390</v>
+        <v>7142733</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651665</v>
+        <v>119651679</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477656</v>
+        <v>477695</v>
       </c>
       <c r="R10" t="n">
-        <v>7143131</v>
+        <v>7143155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1582,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651668</v>
+        <v>119651665</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477695</v>
+        <v>477656</v>
       </c>
       <c r="R11" t="n">
-        <v>7142939</v>
+        <v>7143131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651679</v>
+        <v>119651668</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1758,7 +1758,7 @@
         <v>477695</v>
       </c>
       <c r="R12" t="n">
-        <v>7143155</v>
+        <v>7142939</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -4127,10 +4127,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651706</v>
+        <v>119651641</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4139,25 +4139,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478162</v>
+        <v>477881</v>
       </c>
       <c r="R35" t="n">
-        <v>7142400</v>
+        <v>7142847</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651641</v>
+        <v>119651706</v>
       </c>
       <c r="B36" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4241,25 +4241,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477881</v>
+        <v>478162</v>
       </c>
       <c r="R36" t="n">
-        <v>7142847</v>
+        <v>7142400</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 33262-2024 artfynd.xlsx
+++ b/artfynd/A 33262-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119651678</v>
+        <v>119651709</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477860</v>
+        <v>478183</v>
       </c>
       <c r="R2" t="n">
-        <v>7143097</v>
+        <v>7142390</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119651669</v>
+        <v>119651685</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477624</v>
+        <v>478272</v>
       </c>
       <c r="R3" t="n">
-        <v>7142669</v>
+        <v>7142513</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119651709</v>
+        <v>119651687</v>
       </c>
       <c r="B4" t="n">
-        <v>91128</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478183</v>
+        <v>477885</v>
       </c>
       <c r="R4" t="n">
-        <v>7142390</v>
+        <v>7142877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119651638</v>
+        <v>119651688</v>
       </c>
       <c r="B5" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478188</v>
+        <v>477825</v>
       </c>
       <c r="R5" t="n">
-        <v>7142387</v>
+        <v>7143049</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119651644</v>
+        <v>119651639</v>
       </c>
       <c r="B6" t="n">
-        <v>91254</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477632</v>
+        <v>478102</v>
       </c>
       <c r="R6" t="n">
-        <v>7142733</v>
+        <v>7142644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119651708</v>
+        <v>119651680</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478398</v>
+        <v>477977</v>
       </c>
       <c r="R7" t="n">
-        <v>7142260</v>
+        <v>7142600</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119651707</v>
+        <v>119651641</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478303</v>
+        <v>477881</v>
       </c>
       <c r="R8" t="n">
-        <v>7142341</v>
+        <v>7142847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119651667</v>
+        <v>119651642</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477770</v>
+        <v>477886</v>
       </c>
       <c r="R9" t="n">
-        <v>7143140</v>
+        <v>7142880</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1425,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119651679</v>
+        <v>119651643</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477695</v>
+        <v>477621</v>
       </c>
       <c r="R10" t="n">
-        <v>7143155</v>
+        <v>7142895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,11 +1522,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119651665</v>
+        <v>119651644</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477656</v>
+        <v>477632</v>
       </c>
       <c r="R11" t="n">
-        <v>7143131</v>
+        <v>7142733</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119651668</v>
+        <v>119651645</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477695</v>
+        <v>478034</v>
       </c>
       <c r="R12" t="n">
-        <v>7142939</v>
+        <v>7142532</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1716,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119651705</v>
+        <v>119651646</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478087</v>
+        <v>478074</v>
       </c>
       <c r="R13" t="n">
-        <v>7142484</v>
+        <v>7142501</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119651699</v>
+        <v>119651638</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477616</v>
+        <v>478188</v>
       </c>
       <c r="R14" t="n">
-        <v>7142666</v>
+        <v>7142387</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119651681</v>
+        <v>119651697</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478033</v>
+        <v>478297</v>
       </c>
       <c r="R15" t="n">
-        <v>7142718</v>
+        <v>7142499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119651685</v>
+        <v>119651698</v>
       </c>
       <c r="B16" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478272</v>
+        <v>477862</v>
       </c>
       <c r="R16" t="n">
-        <v>7142513</v>
+        <v>7142754</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,19 +2130,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119651701</v>
+        <v>119651699</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2270,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477873</v>
+        <v>477616</v>
       </c>
       <c r="R17" t="n">
-        <v>7142534</v>
+        <v>7142666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,66 +2227,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119651683</v>
+        <v>119651700</v>
       </c>
       <c r="B18" t="n">
-        <v>57421</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478354</v>
+        <v>477768</v>
       </c>
       <c r="R18" t="n">
-        <v>7142310</v>
+        <v>7142610</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,19 +2324,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119651704</v>
+        <v>119651701</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2490,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478040</v>
+        <v>477873</v>
       </c>
       <c r="R19" t="n">
-        <v>7142457</v>
+        <v>7142534</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2552,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119651671</v>
+        <v>119651702</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478034</v>
+        <v>477946</v>
       </c>
       <c r="R20" t="n">
-        <v>7142454</v>
+        <v>7142571</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,11 +2492,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119651664</v>
+        <v>119651704</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478157</v>
+        <v>478040</v>
       </c>
       <c r="R21" t="n">
-        <v>7142616</v>
+        <v>7142457</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,11 +2589,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2766,37 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119651639</v>
+        <v>119651705</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2806,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478102</v>
+        <v>478087</v>
       </c>
       <c r="R22" t="n">
-        <v>7142644</v>
+        <v>7142484</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2868,37 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119651687</v>
+        <v>119651706</v>
       </c>
       <c r="B23" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2908,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477885</v>
+        <v>478162</v>
       </c>
       <c r="R23" t="n">
-        <v>7142877</v>
+        <v>7142400</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2970,70 +2809,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119651675</v>
+        <v>119651707</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478361</v>
+        <v>478303</v>
       </c>
       <c r="R24" t="n">
-        <v>7142354</v>
+        <v>7142341</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,37 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119651666</v>
+        <v>119651708</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3132,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477775</v>
+        <v>478398</v>
       </c>
       <c r="R25" t="n">
-        <v>7143155</v>
+        <v>7142260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3168,11 +2977,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3199,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119651642</v>
+        <v>119651681</v>
       </c>
       <c r="B26" t="n">
-        <v>91254</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3239,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477886</v>
+        <v>478033</v>
       </c>
       <c r="R26" t="n">
-        <v>7142880</v>
+        <v>7142718</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,37 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119651695</v>
+        <v>119651678</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3341,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477953</v>
+        <v>477860</v>
       </c>
       <c r="R27" t="n">
-        <v>7142946</v>
+        <v>7143097</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3377,6 +3171,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3403,37 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119651700</v>
+        <v>119651679</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3443,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477768</v>
+        <v>477695</v>
       </c>
       <c r="R28" t="n">
-        <v>7142610</v>
+        <v>7143155</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3479,6 +3273,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3505,15 +3304,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119651677</v>
+        <v>119651664</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478328</v>
+        <v>478157</v>
       </c>
       <c r="R29" t="n">
-        <v>7142289</v>
+        <v>7142616</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3612,15 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119651689</v>
+        <v>119651665</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3628,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3652,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478214</v>
+        <v>477656</v>
       </c>
       <c r="R30" t="n">
-        <v>7142533</v>
+        <v>7143131</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3714,15 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119651694</v>
+        <v>119651666</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3730,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3754,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477874</v>
+        <v>477775</v>
       </c>
       <c r="R31" t="n">
-        <v>7142867</v>
+        <v>7143155</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,6 +3574,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3816,37 +3605,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119651645</v>
+        <v>119651667</v>
       </c>
       <c r="B32" t="n">
-        <v>91254</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3856,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478034</v>
+        <v>477770</v>
       </c>
       <c r="R32" t="n">
-        <v>7142532</v>
+        <v>7143140</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3892,6 +3676,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3918,15 +3707,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119651676</v>
+        <v>119651668</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,10 +3742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478329</v>
+        <v>477695</v>
       </c>
       <c r="R33" t="n">
-        <v>7142297</v>
+        <v>7142939</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4025,15 +3809,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119651696</v>
+        <v>119651669</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4041,21 +3820,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4065,10 +3844,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478181</v>
+        <v>477624</v>
       </c>
       <c r="R34" t="n">
-        <v>7142430</v>
+        <v>7142669</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4101,6 +3880,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4127,50 +3911,61 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119651641</v>
+        <v>119651670</v>
       </c>
       <c r="B35" t="n">
-        <v>91254</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477881</v>
+        <v>477861</v>
       </c>
       <c r="R35" t="n">
-        <v>7142847</v>
+        <v>7142701</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4229,15 +4024,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119651706</v>
+        <v>119651671</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4245,21 +4035,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4269,10 +4059,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478162</v>
+        <v>478034</v>
       </c>
       <c r="R36" t="n">
-        <v>7142400</v>
+        <v>7142454</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4305,6 +4095,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4331,37 +4126,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119651646</v>
+        <v>119651674</v>
       </c>
       <c r="B37" t="n">
-        <v>91254</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4371,10 +4161,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478074</v>
+        <v>478153</v>
       </c>
       <c r="R37" t="n">
-        <v>7142501</v>
+        <v>7142438</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4407,6 +4197,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4433,15 +4228,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119651690</v>
+        <v>119651675</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,34 +4239,54 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478032</v>
+        <v>478361</v>
       </c>
       <c r="R38" t="n">
-        <v>7142707</v>
+        <v>7142354</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4535,15 +4345,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119651698</v>
+        <v>119651676</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4551,21 +4356,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4575,10 +4380,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477862</v>
+        <v>478329</v>
       </c>
       <c r="R39" t="n">
-        <v>7142754</v>
+        <v>7142297</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4611,6 +4416,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4637,37 +4447,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119651643</v>
+        <v>119651677</v>
       </c>
       <c r="B40" t="n">
-        <v>91254</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4677,10 +4482,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477621</v>
+        <v>478328</v>
       </c>
       <c r="R40" t="n">
-        <v>7142895</v>
+        <v>7142289</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4713,6 +4518,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4739,15 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119651688</v>
+        <v>119651682</v>
       </c>
       <c r="B41" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4755,34 +4560,50 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477825</v>
+        <v>477848</v>
       </c>
       <c r="R41" t="n">
-        <v>7143049</v>
+        <v>7142542</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4841,15 +4662,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119651697</v>
+        <v>119651683</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4857,34 +4673,50 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fågelvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478297</v>
+        <v>478354</v>
       </c>
       <c r="R42" t="n">
-        <v>7142499</v>
+        <v>7142310</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4940,451 +4772,6 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>119651670</v>
-      </c>
-      <c r="B43" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Fågelvattnet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>477861</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7142701</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>119651674</v>
-      </c>
-      <c r="B44" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Fågelvattnet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>478153</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7142438</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>119651691</v>
-      </c>
-      <c r="B45" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Fågelvattnet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>477857</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7142825</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>119651682</v>
-      </c>
-      <c r="B46" t="n">
-        <v>57421</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Fågelvattnet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>477848</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7142542</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33262-2024 artfynd.xlsx
+++ b/artfynd/A 33262-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651709</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651685</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651687</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651688</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651639</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651680</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651641</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651642</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651643</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651644</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651645</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651646</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651638</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651697</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651698</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651699</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651700</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651701</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651702</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651704</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651705</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651706</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651707</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651708</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651681</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,6 +3329,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651678</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3301,6 +3436,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651679</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3403,6 +3543,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651664</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3500,6 +3645,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651665</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3602,6 +3752,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651666</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3704,6 +3859,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651667</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3806,6 +3966,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651668</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3908,6 +4073,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651669</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4021,6 +4191,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651670</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4123,6 +4298,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651671</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4225,6 +4405,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651674</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4342,6 +4527,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651675</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4444,6 +4634,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651676</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4546,6 +4741,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651677</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4659,6 +4859,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651682</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4772,8 +4977,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651683</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>